--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -206,15 +206,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -251,45 +251,225 @@
     <t>AQUINO</t>
   </si>
   <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MAYAHUA</t>
   </si>
   <si>
@@ -299,90 +479,18 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>PACHECO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
     <t>TETLA</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -392,93 +500,24 @@
     <t>CASTELLANOS</t>
   </si>
   <si>
-    <t>LEPE</t>
-  </si>
-  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
     <t>GUEVARA</t>
   </si>
   <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
     <t>GUADALUPE JOSELYNE</t>
   </si>
   <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
     <t>ZENON AXXEL</t>
   </si>
   <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
     <t>ZURY BETZABE</t>
   </si>
   <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
     <t>MICHEL</t>
   </si>
   <si>
@@ -491,55 +530,16 @@
     <t>VALERIA</t>
   </si>
   <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
     <t>MARIEL</t>
   </si>
   <si>
     <t>ANDREA YONETH</t>
   </si>
   <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
     <t>YAZURI</t>
   </si>
   <si>
     <t>ANIELKA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>7</v>
@@ -1085,7 +1085,7 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
@@ -1185,7 +1185,7 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>7</v>
@@ -1239,7 +1239,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1339,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>7</v>
@@ -1393,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>7</v>
@@ -1416,7 +1416,7 @@
         <v>10</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1470,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1493,7 +1493,7 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
         <v>7</v>
@@ -1547,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1570,7 +1570,7 @@
         <v>6</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1624,7 +1624,7 @@
         <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1647,7 +1647,7 @@
         <v>9</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
         <v>9</v>
@@ -1701,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1724,7 +1724,7 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>8</v>
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1878,7 +1878,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>6</v>
@@ -1932,7 +1932,7 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>7</v>
@@ -2009,7 +2009,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -2032,7 +2032,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>7</v>
@@ -2086,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>7</v>
@@ -2109,7 +2109,7 @@
         <v>10</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>6</v>
@@ -2163,7 +2163,7 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>6</v>
@@ -2263,7 +2263,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>7</v>
@@ -2317,7 +2317,7 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2340,7 +2340,7 @@
         <v>8</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>7</v>
@@ -2394,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2494,7 +2494,7 @@
         <v>9</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>6</v>
@@ -2548,7 +2548,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2571,7 +2571,7 @@
         <v>9</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>8</v>
@@ -2625,7 +2625,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2648,7 +2648,7 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -2702,7 +2702,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2725,7 +2725,7 @@
         <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E26">
         <v>9</v>
@@ -2779,7 +2779,7 @@
         <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2879,7 +2879,7 @@
         <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>8</v>
@@ -2933,7 +2933,7 @@
         <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -2956,7 +2956,7 @@
         <v>8</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>7</v>
@@ -3010,7 +3010,7 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3033,7 +3033,7 @@
         <v>10</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
         <v>7</v>
@@ -3087,7 +3087,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -3110,7 +3110,7 @@
         <v>10</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -3164,7 +3164,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3187,7 +3187,7 @@
         <v>9</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -3241,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W32">
         <v>6</v>
@@ -3264,7 +3264,7 @@
         <v>9</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -3318,7 +3318,7 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>6</v>
@@ -3418,7 +3418,7 @@
         <v>10</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
         <v>8</v>
@@ -3472,7 +3472,7 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3572,7 +3572,7 @@
         <v>7</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -3626,7 +3626,7 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>6</v>
@@ -3649,7 +3649,7 @@
         <v>-1</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E38">
         <v>10</v>
@@ -3703,7 +3703,7 @@
         <v>-1</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W38">
         <v>10</v>
@@ -3726,7 +3726,7 @@
         <v>10</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E39">
         <v>8</v>
@@ -3780,7 +3780,7 @@
         <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W39">
         <v>8</v>
@@ -3803,7 +3803,7 @@
         <v>10</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <v>9</v>
@@ -3857,7 +3857,7 @@
         <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3880,7 +3880,7 @@
         <v>10</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E41">
         <v>7</v>
@@ -3934,7 +3934,7 @@
         <v>10</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>7</v>
@@ -3957,7 +3957,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E42">
         <v>7</v>
@@ -4011,7 +4011,7 @@
         <v>10</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W42">
         <v>7</v>
@@ -4230,7 +4230,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>62</v>
@@ -4239,27 +4239,30 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29.27</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>9.699999999999999</v>
+      </c>
       <c r="I2">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -4268,30 +4271,30 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>29.27</v>
+        <v>73.17</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="J3">
-        <v>70.73</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -4300,25 +4303,25 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>73.17</v>
+        <v>75.61</v>
       </c>
       <c r="G4">
-        <v>9.76</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>17.07</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4424,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4459,33 +4462,33 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920388</v>
+        <v>21330051920029</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>62</v>
@@ -4493,42 +4496,42 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920029</v>
+        <v>21330051920030</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920029</v>
+        <v>21330051920030</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4539,13 +4542,13 @@
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>63</v>
@@ -4553,19 +4556,19 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920030</v>
+        <v>21330051920031</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>62</v>
@@ -4573,19 +4576,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920030</v>
+        <v>21330051920032</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>64</v>
@@ -4593,39 +4596,39 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920031</v>
+        <v>21330051920034</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920031</v>
+        <v>21330051920035</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>62</v>
@@ -4633,19 +4636,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920032</v>
+        <v>21330051920036</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>
@@ -4653,19 +4656,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920033</v>
+        <v>21330051920037</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
@@ -4673,79 +4676,79 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920034</v>
+        <v>21330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920034</v>
+        <v>21330051920038</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920035</v>
+        <v>21330051920390</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920035</v>
+        <v>21330051920039</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -4753,39 +4756,39 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920036</v>
+        <v>21330051920041</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920036</v>
+        <v>21330051920043</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -4793,39 +4796,39 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920037</v>
+        <v>21330051920043</v>
       </c>
       <c r="B19" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D19" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920037</v>
+        <v>21330051920046</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -4833,139 +4836,139 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920038</v>
+        <v>21330051920047</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920038</v>
+        <v>21330051920047</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920390</v>
+        <v>21330051920052</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920390</v>
+        <v>21330051920052</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920039</v>
+        <v>21330051920052</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920039</v>
+        <v>21330051920052</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920040</v>
+        <v>21330051920053</v>
       </c>
       <c r="B27" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
         <v>62</v>
@@ -4973,39 +4976,39 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920041</v>
+        <v>21330051920054</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D28" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920041</v>
+        <v>21330051920057</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>62</v>
@@ -5013,99 +5016,99 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B30" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="D31" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
         <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920045</v>
+        <v>21330051920057</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920046</v>
+        <v>21330051920058</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920046</v>
+        <v>21330051920059</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E34" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
         <v>62</v>
@@ -5113,39 +5116,39 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920047</v>
+        <v>21330051920060</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D35" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920047</v>
+        <v>21330051920061</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
         <v>62</v>
@@ -5153,79 +5156,79 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920048</v>
+        <v>21330051920061</v>
       </c>
       <c r="B37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D37" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920050</v>
+        <v>21330051920061</v>
       </c>
       <c r="B38" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D38" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920049</v>
+        <v>21330051920061</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920051</v>
+        <v>21330051920062</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="D40" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
         <v>62</v>
@@ -5233,19 +5236,19 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920052</v>
+        <v>21330051920062</v>
       </c>
       <c r="B41" t="s">
         <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D41" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F41" t="s">
         <v>63</v>
@@ -5253,39 +5256,39 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920052</v>
+        <v>21330051920065</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D42" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920052</v>
+        <v>21330051920066</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="E43" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F43" t="s">
         <v>62</v>
@@ -5293,119 +5296,119 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920052</v>
+        <v>21330051920067</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E44" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920053</v>
+        <v>21330051920069</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D45" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E45" t="s">
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>21330051920053</v>
+        <v>21330051920069</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="D46" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E46" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920054</v>
+        <v>21330051920069</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D47" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920054</v>
+        <v>21330051920069</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D48" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="E48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F48" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>21330051920055</v>
+        <v>21330051920070</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C49" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D49" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E49" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
         <v>62</v>
@@ -5413,682 +5416,62 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>21330051920056</v>
+        <v>21330051920070</v>
       </c>
       <c r="B50" t="s">
         <v>97</v>
       </c>
       <c r="C50" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>21330051920057</v>
+        <v>21330051920070</v>
       </c>
       <c r="B51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F51" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>21330051920057</v>
+        <v>21330051920070</v>
       </c>
       <c r="B52" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C52" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="D52" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>21330051920057</v>
-      </c>
-      <c r="B53" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" t="s">
-        <v>86</v>
-      </c>
-      <c r="D53" t="s">
-        <v>162</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>21330051920057</v>
-      </c>
-      <c r="B54" t="s">
-        <v>98</v>
-      </c>
-      <c r="C54" t="s">
-        <v>86</v>
-      </c>
-      <c r="D54" t="s">
-        <v>162</v>
-      </c>
-      <c r="E54" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>21330051920058</v>
-      </c>
-      <c r="B55" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" t="s">
-        <v>86</v>
-      </c>
-      <c r="D55" t="s">
-        <v>163</v>
-      </c>
-      <c r="E55" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>21330051920058</v>
-      </c>
-      <c r="B56" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" t="s">
-        <v>86</v>
-      </c>
-      <c r="D56" t="s">
-        <v>163</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>21330051920059</v>
-      </c>
-      <c r="B57" t="s">
-        <v>100</v>
-      </c>
-      <c r="C57" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" t="s">
-        <v>164</v>
-      </c>
-      <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>21330051920059</v>
-      </c>
-      <c r="B58" t="s">
-        <v>100</v>
-      </c>
-      <c r="C58" t="s">
-        <v>127</v>
-      </c>
-      <c r="D58" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>21330051920060</v>
-      </c>
-      <c r="B59" t="s">
-        <v>98</v>
-      </c>
-      <c r="C59" t="s">
-        <v>128</v>
-      </c>
-      <c r="D59" t="s">
-        <v>165</v>
-      </c>
-      <c r="E59" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>21330051920060</v>
-      </c>
-      <c r="B60" t="s">
-        <v>98</v>
-      </c>
-      <c r="C60" t="s">
-        <v>128</v>
-      </c>
-      <c r="D60" t="s">
-        <v>165</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>21330051920061</v>
-      </c>
-      <c r="B61" t="s">
-        <v>101</v>
-      </c>
-      <c r="C61" t="s">
-        <v>129</v>
-      </c>
-      <c r="D61" t="s">
-        <v>166</v>
-      </c>
-      <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>21330051920061</v>
-      </c>
-      <c r="B62" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" t="s">
-        <v>129</v>
-      </c>
-      <c r="D62" t="s">
-        <v>166</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>21330051920061</v>
-      </c>
-      <c r="B63" t="s">
-        <v>101</v>
-      </c>
-      <c r="C63" t="s">
-        <v>129</v>
-      </c>
-      <c r="D63" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>21330051920061</v>
-      </c>
-      <c r="B64" t="s">
-        <v>101</v>
-      </c>
-      <c r="C64" t="s">
-        <v>129</v>
-      </c>
-      <c r="D64" t="s">
-        <v>166</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>21330051920062</v>
-      </c>
-      <c r="B65" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" t="s">
-        <v>98</v>
-      </c>
-      <c r="D65" t="s">
-        <v>167</v>
-      </c>
-      <c r="E65" t="s">
-        <v>9</v>
-      </c>
-      <c r="F65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>21330051920062</v>
-      </c>
-      <c r="B66" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66" t="s">
-        <v>98</v>
-      </c>
-      <c r="D66" t="s">
-        <v>167</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>21330051920062</v>
-      </c>
-      <c r="B67" t="s">
-        <v>102</v>
-      </c>
-      <c r="C67" t="s">
-        <v>98</v>
-      </c>
-      <c r="D67" t="s">
-        <v>167</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>21330051920063</v>
-      </c>
-      <c r="B68" t="s">
-        <v>103</v>
-      </c>
-      <c r="C68" t="s">
-        <v>130</v>
-      </c>
-      <c r="D68" t="s">
-        <v>168</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>21330051920064</v>
-      </c>
-      <c r="B69" t="s">
-        <v>104</v>
-      </c>
-      <c r="C69" t="s">
-        <v>83</v>
-      </c>
-      <c r="D69" t="s">
-        <v>169</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>21330051920065</v>
-      </c>
-      <c r="B70" t="s">
-        <v>105</v>
-      </c>
-      <c r="C70" t="s">
-        <v>119</v>
-      </c>
-      <c r="D70" t="s">
-        <v>170</v>
-      </c>
-      <c r="E70" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>21330051920065</v>
-      </c>
-      <c r="B71" t="s">
-        <v>105</v>
-      </c>
-      <c r="C71" t="s">
-        <v>119</v>
-      </c>
-      <c r="D71" t="s">
-        <v>170</v>
-      </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>21330051920066</v>
-      </c>
-      <c r="B72" t="s">
-        <v>105</v>
-      </c>
-      <c r="C72" t="s">
-        <v>131</v>
-      </c>
-      <c r="D72" t="s">
-        <v>164</v>
-      </c>
-      <c r="E72" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>21330051920066</v>
-      </c>
-      <c r="B73" t="s">
-        <v>105</v>
-      </c>
-      <c r="C73" t="s">
-        <v>131</v>
-      </c>
-      <c r="D73" t="s">
-        <v>164</v>
-      </c>
-      <c r="E73" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>21330051920067</v>
-      </c>
-      <c r="B74" t="s">
-        <v>106</v>
-      </c>
-      <c r="C74" t="s">
-        <v>132</v>
-      </c>
-      <c r="D74" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>21330051920067</v>
-      </c>
-      <c r="B75" t="s">
-        <v>106</v>
-      </c>
-      <c r="C75" t="s">
-        <v>132</v>
-      </c>
-      <c r="D75" t="s">
-        <v>171</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>21330051920069</v>
-      </c>
-      <c r="B76" t="s">
-        <v>107</v>
-      </c>
-      <c r="C76" t="s">
-        <v>97</v>
-      </c>
-      <c r="D76" t="s">
-        <v>172</v>
-      </c>
-      <c r="E76" t="s">
-        <v>9</v>
-      </c>
-      <c r="F76" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>21330051920069</v>
-      </c>
-      <c r="B77" t="s">
-        <v>107</v>
-      </c>
-      <c r="C77" t="s">
-        <v>97</v>
-      </c>
-      <c r="D77" t="s">
-        <v>172</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>21330051920069</v>
-      </c>
-      <c r="B78" t="s">
-        <v>107</v>
-      </c>
-      <c r="C78" t="s">
-        <v>97</v>
-      </c>
-      <c r="D78" t="s">
-        <v>172</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>21330051920069</v>
-      </c>
-      <c r="B79" t="s">
-        <v>107</v>
-      </c>
-      <c r="C79" t="s">
-        <v>97</v>
-      </c>
-      <c r="D79" t="s">
-        <v>172</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>21330051920070</v>
-      </c>
-      <c r="B80" t="s">
-        <v>108</v>
-      </c>
-      <c r="C80" t="s">
-        <v>133</v>
-      </c>
-      <c r="D80" t="s">
-        <v>173</v>
-      </c>
-      <c r="E80" t="s">
-        <v>9</v>
-      </c>
-      <c r="F80" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>21330051920070</v>
-      </c>
-      <c r="B81" t="s">
-        <v>108</v>
-      </c>
-      <c r="C81" t="s">
-        <v>133</v>
-      </c>
-      <c r="D81" t="s">
-        <v>173</v>
-      </c>
-      <c r="E81" t="s">
-        <v>8</v>
-      </c>
-      <c r="F81" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>21330051920070</v>
-      </c>
-      <c r="B82" t="s">
-        <v>108</v>
-      </c>
-      <c r="C82" t="s">
-        <v>133</v>
-      </c>
-      <c r="D82" t="s">
-        <v>173</v>
-      </c>
-      <c r="E82" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>21330051920070</v>
-      </c>
-      <c r="B83" t="s">
-        <v>108</v>
-      </c>
-      <c r="C83" t="s">
-        <v>133</v>
-      </c>
-      <c r="D83" t="s">
-        <v>173</v>
-      </c>
-      <c r="E83" t="s">
-        <v>6</v>
-      </c>
-      <c r="F83" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6127,13 +5510,13 @@
         <v>21330051920052</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -6144,13 +5527,13 @@
         <v>21330051920057</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -6161,13 +5544,13 @@
         <v>21330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -6178,13 +5561,13 @@
         <v>21330051920069</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -6195,13 +5578,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="E6">
         <v>4</v>
@@ -6215,10 +5598,10 @@
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -6226,33 +5609,33 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920062</v>
+        <v>21330051920038</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920388</v>
+        <v>21330051920043</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -6260,16 +5643,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920029</v>
+        <v>21330051920047</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -6277,16 +5660,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920031</v>
+        <v>21330051920062</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -6294,339 +5677,339 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920034</v>
+        <v>21330051920388</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920035</v>
+        <v>21330051920029</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920036</v>
+        <v>21330051920031</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920037</v>
+        <v>21330051920032</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920038</v>
+        <v>21330051920034</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920390</v>
+        <v>21330051920035</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920039</v>
+        <v>21330051920036</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920041</v>
+        <v>21330051920037</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920043</v>
+        <v>21330051920390</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920046</v>
+        <v>21330051920039</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920047</v>
+        <v>21330051920041</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920053</v>
+        <v>21330051920046</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920054</v>
+        <v>21330051920053</v>
       </c>
       <c r="B24" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920058</v>
+        <v>21330051920054</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920059</v>
+        <v>21330051920058</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C26" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920060</v>
+        <v>21330051920059</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920065</v>
+        <v>21330051920060</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920066</v>
+        <v>21330051920065</v>
       </c>
       <c r="B29" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920067</v>
+        <v>21330051920066</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920032</v>
+        <v>21330051920067</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -6637,16 +6020,16 @@
         <v>21330051920033</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -6654,16 +6037,16 @@
         <v>21330051920040</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>149</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -6671,16 +6054,16 @@
         <v>21330051920045</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D34" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -6688,16 +6071,16 @@
         <v>21330051920048</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>121</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -6705,16 +6088,16 @@
         <v>21330051920050</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -6722,16 +6105,16 @@
         <v>21330051920049</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -6739,16 +6122,16 @@
         <v>21330051920051</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>152</v>
       </c>
       <c r="C38" t="s">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -6756,16 +6139,16 @@
         <v>21330051920055</v>
       </c>
       <c r="B39" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -6773,16 +6156,16 @@
         <v>21330051920056</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -6790,16 +6173,16 @@
         <v>21330051920063</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -6807,16 +6190,16 @@
         <v>21330051920064</v>
       </c>
       <c r="B42" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6826,7 +6209,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6858,45 +6241,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920388</v>
+        <v>21330051920032</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920388</v>
+        <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6904,45 +6287,45 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920029</v>
+        <v>21330051920037</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920029</v>
+        <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -6950,22 +6333,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920031</v>
+        <v>21330051920038</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -6973,22 +6356,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920031</v>
+        <v>21330051920038</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -6996,42 +6379,42 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920032</v>
+        <v>21330051920043</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920032</v>
+        <v>21330051920043</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
@@ -7042,45 +6425,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920034</v>
+        <v>21330051920053</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920034</v>
+        <v>21330051920053</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -7088,22 +6471,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920035</v>
+        <v>21330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -7111,22 +6494,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920035</v>
+        <v>21330051920062</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -7134,19 +6517,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920036</v>
+        <v>21330051920388</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -7157,22 +6540,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920036</v>
+        <v>21330051920029</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -7180,19 +6563,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920038</v>
+        <v>21330051920031</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -7203,22 +6586,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920038</v>
+        <v>21330051920034</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -7226,19 +6609,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920390</v>
+        <v>21330051920035</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -7249,22 +6632,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920390</v>
+        <v>21330051920036</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -7272,19 +6655,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920039</v>
+        <v>21330051920390</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -7298,19 +6681,19 @@
         <v>21330051920039</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -7321,16 +6704,16 @@
         <v>21330051920041</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
         <v>62</v>
@@ -7341,22 +6724,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920041</v>
+        <v>21330051920046</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -7364,65 +6747,65 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920043</v>
+        <v>21330051920048</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>118</v>
+        <v>157</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920043</v>
+        <v>21330051920051</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
         <v>63</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920046</v>
+        <v>21330051920054</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
         <v>62</v>
@@ -7433,22 +6816,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>21330051920046</v>
+        <v>21330051920058</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G27">
         <v>-1</v>
@@ -7456,42 +6839,42 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>21330051920048</v>
+        <v>21330051920059</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>21330051920048</v>
+        <v>21330051920060</v>
       </c>
       <c r="B29" t="s">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>62</v>
@@ -7502,42 +6885,42 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>21330051920051</v>
+        <v>21330051920065</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="E30" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>21330051920051</v>
+        <v>21330051920066</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
         <v>62</v>
@@ -7548,530 +6931,24 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>21330051920054</v>
+        <v>21330051920067</v>
       </c>
       <c r="B32" t="s">
         <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="E32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
         <v>62</v>
       </c>
       <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>21330051920054</v>
-      </c>
-      <c r="B33" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" t="s">
-        <v>159</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>63</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>21330051920058</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" t="s">
-        <v>163</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>21330051920058</v>
-      </c>
-      <c r="B35" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" t="s">
-        <v>63</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>21330051920059</v>
-      </c>
-      <c r="B36" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>21330051920059</v>
-      </c>
-      <c r="B37" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" t="s">
-        <v>127</v>
-      </c>
-      <c r="D37" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>63</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>21330051920060</v>
-      </c>
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" t="s">
-        <v>128</v>
-      </c>
-      <c r="D38" t="s">
-        <v>165</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>21330051920060</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>63</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>21330051920065</v>
-      </c>
-      <c r="B40" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D40" t="s">
-        <v>170</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>21330051920065</v>
-      </c>
-      <c r="B41" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" t="s">
-        <v>119</v>
-      </c>
-      <c r="D41" t="s">
-        <v>170</v>
-      </c>
-      <c r="E41" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" t="s">
-        <v>63</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>21330051920066</v>
-      </c>
-      <c r="B42" t="s">
-        <v>105</v>
-      </c>
-      <c r="C42" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42" t="s">
-        <v>164</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>62</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>21330051920066</v>
-      </c>
-      <c r="B43" t="s">
-        <v>105</v>
-      </c>
-      <c r="C43" t="s">
-        <v>131</v>
-      </c>
-      <c r="D43" t="s">
-        <v>164</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>63</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>21330051920067</v>
-      </c>
-      <c r="B44" t="s">
-        <v>106</v>
-      </c>
-      <c r="C44" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" t="s">
-        <v>171</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>62</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>21330051920067</v>
-      </c>
-      <c r="B45" t="s">
-        <v>106</v>
-      </c>
-      <c r="C45" t="s">
-        <v>132</v>
-      </c>
-      <c r="D45" t="s">
-        <v>171</v>
-      </c>
-      <c r="E45" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>63</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>21330051920033</v>
-      </c>
-      <c r="B46" t="s">
-        <v>77</v>
-      </c>
-      <c r="C46" t="s">
-        <v>111</v>
-      </c>
-      <c r="D46" t="s">
-        <v>139</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>62</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>21330051920040</v>
-      </c>
-      <c r="B47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" t="s">
-        <v>105</v>
-      </c>
-      <c r="D47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>21330051920045</v>
-      </c>
-      <c r="B48" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" t="s">
-        <v>119</v>
-      </c>
-      <c r="D48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>21330051920050</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" t="s">
-        <v>122</v>
-      </c>
-      <c r="D49" t="s">
-        <v>154</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>62</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
-        <v>21330051920049</v>
-      </c>
-      <c r="B50" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" t="s">
-        <v>89</v>
-      </c>
-      <c r="D50" t="s">
-        <v>155</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>62</v>
-      </c>
-      <c r="G50">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51">
-        <v>21330051920055</v>
-      </c>
-      <c r="B51" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" t="s">
-        <v>160</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>62</v>
-      </c>
-      <c r="G51">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52">
-        <v>21330051920056</v>
-      </c>
-      <c r="B52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" t="s">
-        <v>126</v>
-      </c>
-      <c r="D52" t="s">
-        <v>161</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>62</v>
-      </c>
-      <c r="G52">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53">
-        <v>21330051920063</v>
-      </c>
-      <c r="B53" t="s">
-        <v>103</v>
-      </c>
-      <c r="C53" t="s">
-        <v>130</v>
-      </c>
-      <c r="D53" t="s">
-        <v>168</v>
-      </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
-        <v>62</v>
-      </c>
-      <c r="G53">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54">
-        <v>21330051920064</v>
-      </c>
-      <c r="B54" t="s">
-        <v>104</v>
-      </c>
-      <c r="C54" t="s">
-        <v>83</v>
-      </c>
-      <c r="D54" t="s">
-        <v>169</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>62</v>
-      </c>
-      <c r="G54">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -2805,7 +2805,7 @@
         <v>-1</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F27">
         <v>-1</v>
@@ -2859,7 +2859,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>-1</v>
@@ -4037,7 +4037,7 @@
         <v>-1</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F43">
         <v>-1</v>
@@ -4091,7 +4091,7 @@
         <v>-1</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X43">
         <v>-1</v>
@@ -4114,7 +4114,7 @@
         <v>-1</v>
       </c>
       <c r="E44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F44">
         <v>-1</v>
@@ -4168,7 +4168,7 @@
         <v>-1</v>
       </c>
       <c r="W44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X44">
         <v>-1</v>
@@ -4399,25 +4399,25 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>87.8</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J7">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
     </row>
   </sheetData>
@@ -4427,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4908,10 +4908,10 @@
         <v>135</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4928,44 +4928,44 @@
         <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920053</v>
+        <v>21330051920054</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -4976,16 +4976,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920054</v>
+        <v>21330051920057</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E28" t="s">
         <v>9</v>
@@ -5008,10 +5008,10 @@
         <v>138</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -5028,10 +5028,10 @@
         <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -5048,44 +5048,44 @@
         <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920057</v>
+        <v>21330051920058</v>
       </c>
       <c r="B32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
         <v>99</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920058</v>
+        <v>21330051920059</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -5096,16 +5096,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920059</v>
+        <v>21330051920060</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -5116,16 +5116,16 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>21330051920060</v>
+        <v>21330051920061</v>
       </c>
       <c r="B35" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
@@ -5148,10 +5148,10 @@
         <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -5168,10 +5168,10 @@
         <v>142</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -5188,30 +5188,30 @@
         <v>142</v>
       </c>
       <c r="E38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C39" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E39" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -5228,44 +5228,44 @@
         <v>143</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920062</v>
+        <v>21330051920065</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C41" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="D41" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E41" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920065</v>
+        <v>21330051920066</v>
       </c>
       <c r="B42" t="s">
         <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D42" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E42" t="s">
         <v>9</v>
@@ -5276,16 +5276,16 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920066</v>
+        <v>21330051920067</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D43" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -5296,16 +5296,16 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920067</v>
+        <v>21330051920069</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E44" t="s">
         <v>9</v>
@@ -5328,10 +5328,10 @@
         <v>146</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -5348,50 +5348,50 @@
         <v>146</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E47" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E48" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -5408,69 +5408,9 @@
         <v>147</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F49" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>21330051920070</v>
-      </c>
-      <c r="B50" t="s">
-        <v>97</v>
-      </c>
-      <c r="C50" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>21330051920070</v>
-      </c>
-      <c r="B51" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" t="s">
-        <v>147</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>21330051920070</v>
-      </c>
-      <c r="B52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" t="s">
-        <v>118</v>
-      </c>
-      <c r="D52" t="s">
-        <v>147</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
         <v>63</v>
       </c>
     </row>
@@ -5507,16 +5447,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920052</v>
+        <v>21330051920057</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -5524,16 +5464,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5541,67 +5481,67 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920061</v>
+        <v>21330051920030</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920069</v>
+        <v>21330051920052</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920070</v>
+        <v>21330051920069</v>
       </c>
       <c r="B6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920030</v>
+        <v>21330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="E7">
         <v>3</v>

--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -209,15 +209,15 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -365,148 +365,148 @@
     <t>GALEOTE</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>GUADALUPE JOSELYNE</t>
@@ -1043,7 +1043,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1079,7 +1079,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>10</v>
@@ -1120,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1197,7 +1197,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1274,7 +1274,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1351,7 +1351,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1387,7 +1387,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>8</v>
@@ -1428,7 +1428,7 @@
         <v>10</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1505,7 +1505,7 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1618,7 +1618,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1659,7 +1659,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1736,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1772,7 +1772,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1813,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1849,7 +1849,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1890,7 +1890,7 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1926,7 +1926,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1967,7 +1967,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2003,7 +2003,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>10</v>
@@ -2044,7 +2044,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2121,7 +2121,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2192,13 +2192,13 @@
         <v>8</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G19">
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2234,7 +2234,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2246,7 +2246,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2275,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2311,7 +2311,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2352,7 +2352,7 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2388,7 +2388,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>8</v>
@@ -2429,7 +2429,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2438,7 +2438,7 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
         <v>-1</v>
@@ -2474,7 +2474,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X22">
         <v>-1</v>
@@ -2506,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2583,7 +2583,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2619,7 +2619,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2660,7 +2660,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2737,7 +2737,7 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2814,7 +2814,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2850,7 +2850,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -2891,7 +2891,7 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2927,7 +2927,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2968,7 +2968,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3045,7 +3045,7 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3122,7 +3122,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3199,7 +3199,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3208,7 +3208,7 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3235,7 +3235,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>9</v>
@@ -3244,7 +3244,7 @@
         <v>6</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>-1</v>
@@ -3276,7 +3276,7 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3312,7 +3312,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3344,7 +3344,7 @@
         <v>-1</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F34">
         <v>-1</v>
@@ -3353,7 +3353,7 @@
         <v>5</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3398,7 +3398,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X34">
         <v>-1</v>
@@ -3430,7 +3430,7 @@
         <v>9</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3466,7 +3466,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3498,7 +3498,7 @@
         <v>-1</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F36">
         <v>-1</v>
@@ -3507,7 +3507,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3552,7 +3552,7 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>-1</v>
@@ -3584,7 +3584,7 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3620,7 +3620,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3661,7 +3661,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3670,7 +3670,7 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>-1</v>
@@ -3738,7 +3738,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3774,7 +3774,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U39">
         <v>10</v>
@@ -3815,7 +3815,7 @@
         <v>10</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -3824,7 +3824,7 @@
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>-1</v>
@@ -3851,7 +3851,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>10</v>
@@ -3860,7 +3860,7 @@
         <v>6</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>-1</v>
@@ -3892,7 +3892,7 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I41">
         <v>-1</v>
@@ -3928,7 +3928,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U41">
         <v>10</v>
@@ -3963,13 +3963,13 @@
         <v>7</v>
       </c>
       <c r="F42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G42">
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -4017,7 +4017,7 @@
         <v>7</v>
       </c>
       <c r="X42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>10</v>
@@ -4046,7 +4046,7 @@
         <v>5</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I43">
         <v>-1</v>
@@ -4123,7 +4123,7 @@
         <v>5</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I44">
         <v>-1</v>
@@ -4159,7 +4159,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U44">
         <v>-1</v>
@@ -4239,30 +4239,30 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29.27</v>
+        <v>34.15</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J2">
-        <v>70.73</v>
+        <v>65.84999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -4274,27 +4274,27 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>73.17</v>
       </c>
       <c r="G3">
-        <v>9.76</v>
+        <v>26.83</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -4303,30 +4303,30 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>75.61</v>
+        <v>73.17</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -4335,25 +4335,25 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>82.93000000000001</v>
+        <v>75.61</v>
       </c>
       <c r="G5">
-        <v>17.07</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>24.39</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4402,22 +4402,22 @@
         <v>37</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>90.23999999999999</v>
       </c>
       <c r="G7">
-        <v>4.88</v>
+        <v>9.76</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4427,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4465,7 +4465,7 @@
         <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4485,7 +4485,7 @@
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4505,7 +4505,7 @@
         <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -4525,13 +4525,13 @@
         <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4545,13 +4545,13 @@
         <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4565,7 +4565,7 @@
         <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4585,13 +4585,13 @@
         <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4605,7 +4605,7 @@
         <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -4625,7 +4625,7 @@
         <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -4645,7 +4645,7 @@
         <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -4665,7 +4665,7 @@
         <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -4685,7 +4685,7 @@
         <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -4705,13 +4705,13 @@
         <v>105</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4725,7 +4725,7 @@
         <v>106</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -4745,7 +4745,7 @@
         <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -4765,7 +4765,7 @@
         <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -4785,44 +4785,44 @@
         <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920043</v>
+        <v>21330051920046</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920046</v>
+        <v>21330051920047</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D20" t="s">
         <v>133</v>
@@ -4845,33 +4845,33 @@
         <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920047</v>
+        <v>21330051920052</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
         <v>134</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4885,13 +4885,13 @@
         <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -4905,10 +4905,10 @@
         <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
@@ -4916,33 +4916,33 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D25" t="s">
         <v>135</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920053</v>
+        <v>21330051920054</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
         <v>136</v>
@@ -4956,13 +4956,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920054</v>
+        <v>21330051920057</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D27" t="s">
         <v>137</v>
@@ -4985,13 +4985,13 @@
         <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -5005,21 +5005,21 @@
         <v>99</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920057</v>
+        <v>21330051920058</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
         <v>99</v>
@@ -5028,44 +5028,44 @@
         <v>138</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920057</v>
+        <v>21330051920059</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E31" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>21330051920058</v>
+        <v>21330051920060</v>
       </c>
       <c r="B32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -5076,16 +5076,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>21330051920059</v>
+        <v>21330051920061</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
         <v>9</v>
@@ -5096,22 +5096,22 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>21330051920060</v>
+        <v>21330051920061</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
         <v>141</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -5125,50 +5125,50 @@
         <v>113</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D36" t="s">
         <v>142</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C37" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="D37" t="s">
         <v>142</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F37" t="s">
         <v>64</v>
@@ -5176,36 +5176,36 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>21330051920061</v>
+        <v>21330051920065</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="D39" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -5216,76 +5216,76 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>21330051920062</v>
+        <v>21330051920069</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C40" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="D40" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>21330051920065</v>
+        <v>21330051920069</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>21330051920066</v>
+        <v>21330051920069</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>21330051920067</v>
+        <v>21330051920070</v>
       </c>
       <c r="B43" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E43" t="s">
         <v>9</v>
@@ -5296,10 +5296,10 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B44" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
         <v>117</v>
@@ -5308,18 +5308,18 @@
         <v>146</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
         <v>117</v>
@@ -5328,90 +5328,10 @@
         <v>146</v>
       </c>
       <c r="E45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F45" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>21330051920069</v>
-      </c>
-      <c r="B46" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" t="s">
-        <v>117</v>
-      </c>
-      <c r="D46" t="s">
-        <v>146</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>21330051920070</v>
-      </c>
-      <c r="B47" t="s">
-        <v>97</v>
-      </c>
-      <c r="C47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D47" t="s">
-        <v>147</v>
-      </c>
-      <c r="E47" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>21330051920070</v>
-      </c>
-      <c r="B48" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" t="s">
-        <v>118</v>
-      </c>
-      <c r="D48" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>21330051920070</v>
-      </c>
-      <c r="B49" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" t="s">
-        <v>147</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -5447,50 +5367,50 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920057</v>
+        <v>21330051920030</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920061</v>
+        <v>21330051920052</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920030</v>
+        <v>21330051920057</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5498,16 +5418,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920052</v>
+        <v>21330051920061</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5521,10 +5441,10 @@
         <v>96</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5538,10 +5458,10 @@
         <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -5558,7 +5478,7 @@
         <v>105</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -5566,16 +5486,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920043</v>
+        <v>21330051920047</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -5583,16 +5503,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920047</v>
+        <v>21330051920062</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5600,30 +5520,30 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920062</v>
+        <v>21330051920388</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920388</v>
+        <v>21330051920029</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
         <v>119</v>
@@ -5634,16 +5554,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920029</v>
+        <v>21330051920031</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5651,13 +5571,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920031</v>
+        <v>21330051920032</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
         <v>122</v>
@@ -5668,13 +5588,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920032</v>
+        <v>21330051920034</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D15" t="s">
         <v>123</v>
@@ -5685,13 +5605,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920034</v>
+        <v>21330051920035</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D16" t="s">
         <v>124</v>
@@ -5702,13 +5622,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920035</v>
+        <v>21330051920036</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
         <v>125</v>
@@ -5719,13 +5639,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>126</v>
@@ -5736,16 +5656,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920037</v>
+        <v>21330051920390</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5753,13 +5673,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920390</v>
+        <v>21330051920039</v>
       </c>
       <c r="B20" t="s">
         <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
         <v>129</v>
@@ -5770,10 +5690,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920039</v>
+        <v>21330051920041</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
         <v>107</v>
@@ -5787,13 +5707,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920041</v>
+        <v>21330051920043</v>
       </c>
       <c r="B22" t="s">
         <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
         <v>131</v>
@@ -5813,7 +5733,7 @@
         <v>109</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -5830,7 +5750,7 @@
         <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5847,7 +5767,7 @@
         <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -5864,7 +5784,7 @@
         <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -5881,7 +5801,7 @@
         <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -5898,7 +5818,7 @@
         <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -5915,7 +5835,7 @@
         <v>114</v>
       </c>
       <c r="D29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E29">
         <v>1</v>
@@ -5923,16 +5843,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920066</v>
+        <v>21330051920067</v>
       </c>
       <c r="B30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
         <v>115</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -5940,33 +5860,33 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920067</v>
+        <v>21330051920033</v>
       </c>
       <c r="B31" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>155</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920033</v>
+        <v>21330051920040</v>
       </c>
       <c r="B32" t="s">
         <v>148</v>
       </c>
       <c r="C32" t="s">
-        <v>156</v>
+        <v>94</v>
       </c>
       <c r="D32" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5974,16 +5894,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920040</v>
+        <v>21330051920045</v>
       </c>
       <c r="B33" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="D33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5991,16 +5911,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920045</v>
+        <v>21330051920048</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -6008,16 +5928,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920048</v>
+        <v>21330051920050</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="C35" t="s">
         <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -6025,16 +5945,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920050</v>
+        <v>21330051920049</v>
       </c>
       <c r="B36" t="s">
         <v>150</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -6042,16 +5962,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920049</v>
+        <v>21330051920051</v>
       </c>
       <c r="B37" t="s">
         <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
       <c r="D37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -6059,7 +5979,7 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920051</v>
+        <v>21330051920055</v>
       </c>
       <c r="B38" t="s">
         <v>152</v>
@@ -6068,7 +5988,7 @@
         <v>159</v>
       </c>
       <c r="D38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -6076,16 +5996,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920055</v>
+        <v>21330051920056</v>
       </c>
       <c r="B39" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
         <v>160</v>
       </c>
       <c r="D39" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -6093,16 +6013,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920056</v>
+        <v>21330051920063</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C40" t="s">
         <v>161</v>
       </c>
       <c r="D40" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -6110,16 +6030,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920063</v>
+        <v>21330051920064</v>
       </c>
       <c r="B41" t="s">
         <v>154</v>
       </c>
       <c r="C41" t="s">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="D41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -6127,16 +6047,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920064</v>
+        <v>21330051920066</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>82</v>
+        <v>162</v>
       </c>
       <c r="D42" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -6149,7 +6069,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6190,13 +6110,13 @@
         <v>99</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6213,13 +6133,13 @@
         <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -6236,13 +6156,13 @@
         <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6259,7 +6179,7 @@
         <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6273,19 +6193,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920038</v>
+        <v>21330051920062</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
@@ -6296,16 +6216,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920038</v>
+        <v>21330051920062</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6319,22 +6239,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920043</v>
+        <v>21330051920388</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -6342,16 +6262,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920043</v>
+        <v>21330051920029</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -6365,39 +6285,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920053</v>
+        <v>21330051920031</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920053</v>
+        <v>21330051920034</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -6411,22 +6331,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920062</v>
+        <v>21330051920035</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D12" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -6434,16 +6354,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920062</v>
+        <v>21330051920036</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -6457,16 +6377,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920388</v>
+        <v>21330051920390</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -6480,16 +6400,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920029</v>
+        <v>21330051920039</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -6503,16 +6423,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920031</v>
+        <v>21330051920041</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -6526,22 +6446,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920034</v>
+        <v>21330051920043</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -6549,16 +6469,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920035</v>
+        <v>21330051920046</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -6572,62 +6492,62 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>21330051920036</v>
+        <v>21330051920048</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>21330051920390</v>
+        <v>21330051920051</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>21330051920039</v>
+        <v>21330051920054</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -6641,16 +6561,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>21330051920041</v>
+        <v>21330051920058</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
@@ -6664,16 +6584,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>21330051920046</v>
+        <v>21330051920059</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -6687,62 +6607,62 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>21330051920048</v>
+        <v>21330051920060</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>21330051920051</v>
+        <v>21330051920065</v>
       </c>
       <c r="B25" t="s">
-        <v>152</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>21330051920054</v>
+        <v>21330051920067</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -6751,144 +6671,6 @@
         <v>62</v>
       </c>
       <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>21330051920058</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>21330051920059</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>21330051920060</v>
-      </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E29" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>21330051920065</v>
-      </c>
-      <c r="B30" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" t="s">
-        <v>144</v>
-      </c>
-      <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>21330051920066</v>
-      </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" t="s">
-        <v>140</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>21330051920067</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" t="s">
-        <v>145</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-      <c r="G32">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -218,12 +218,12 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -236,121 +236,232 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>COMIHUA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>ARAGON</t>
   </si>
   <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
     <t>AGUILAR</t>
   </si>
   <si>
     <t>AQUINO</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>COMIHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
   </si>
   <si>
     <t>ROMANOS</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
     <t>BRUNO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
     <t>CELESTINO</t>
   </si>
   <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>LEPE</t>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
   </si>
   <si>
     <t>TEZOCO</t>
@@ -359,82 +470,61 @@
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
   </si>
   <si>
     <t>JONATHAN YOSEF</t>
   </si>
   <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
     <t>ALESSANDRA</t>
   </si>
   <si>
     <t>BETSI JOSELIN</t>
   </si>
   <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
     <t>ELIZABETH</t>
   </si>
   <si>
     <t>GABRIELA ELIZABETH</t>
   </si>
   <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
     <t>ZAYRA</t>
   </si>
   <si>
     <t>KARLA JIMENA</t>
   </si>
   <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
+    <t>ZENON AXXEL</t>
   </si>
   <si>
     <t>EMMANUEL DAVID</t>
   </si>
   <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>AMY</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ANDREA YONETH</t>
   </si>
   <si>
     <t>DANIELA</t>
@@ -443,103 +533,13 @@
     <t>SARAHI</t>
   </si>
   <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>ANIELKA</t>
   </si>
   <si>
     <t>XIMENA</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>AMY</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>ANIELKA</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G4">
         <v>10</v>
@@ -1046,19 +1046,19 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1082,19 +1082,19 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1200,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -1236,7 +1236,7 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1262,7 +1262,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>6</v>
@@ -1277,13 +1277,13 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1313,13 +1313,13 @@
         <v>5</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1345,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="F8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G8">
         <v>10</v>
@@ -1354,16 +1354,16 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1390,16 +1390,16 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1431,19 +1431,19 @@
         <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>7</v>
       </c>
       <c r="F10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G10">
         <v>10</v>
@@ -1508,19 +1508,19 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1550,10 +1550,10 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>10</v>
@@ -1585,10 +1585,10 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1621,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1630,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y11">
         <v>10</v>
@@ -1662,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1698,7 +1698,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1739,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1801,13 +1801,13 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>8</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>8</v>
@@ -1816,19 +1816,19 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1855,16 +1855,16 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1884,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="F15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>10</v>
@@ -1893,19 +1893,19 @@
         <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1935,10 +1935,10 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1970,13 +1970,13 @@
         <v>5</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -2006,13 +2006,13 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>-1</v>
@@ -2047,19 +2047,19 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2083,7 +2083,7 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>6</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2124,13 +2124,13 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2160,13 +2160,13 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X18">
         <v>-1</v>
@@ -2186,7 +2186,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E19">
         <v>8</v>
@@ -2201,19 +2201,19 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2237,13 +2237,13 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2278,19 +2278,19 @@
         <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2355,19 +2355,19 @@
         <v>6</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2391,7 +2391,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2432,7 +2432,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2444,7 +2444,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2480,7 +2480,7 @@
         <v>-1</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2509,13 +2509,13 @@
         <v>6</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2551,7 +2551,7 @@
         <v>6</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2586,19 +2586,19 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2663,19 +2663,19 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2702,7 +2702,7 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2740,19 +2740,19 @@
         <v>9</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2776,13 +2776,13 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2823,7 +2823,7 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2894,7 +2894,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2971,13 +2971,13 @@
         <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -3013,7 +3013,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>-1</v>
@@ -3048,19 +3048,19 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3090,7 +3090,7 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -3125,19 +3125,19 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3167,13 +3167,13 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3202,7 +3202,7 @@
         <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3214,7 +3214,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3270,7 +3270,7 @@
         <v>6</v>
       </c>
       <c r="F33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G33">
         <v>10</v>
@@ -3279,16 +3279,16 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3321,10 +3321,10 @@
         <v>6</v>
       </c>
       <c r="W33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3338,7 +3338,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>-1</v>
@@ -3356,7 +3356,7 @@
         <v>5</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3392,7 +3392,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -3424,7 +3424,7 @@
         <v>8</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G35">
         <v>9</v>
@@ -3433,19 +3433,19 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3478,10 +3478,10 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3516,7 +3516,7 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3587,19 +3587,19 @@
         <v>6</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3623,19 +3623,19 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>6</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3646,7 +3646,7 @@
         <v>8</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -3664,7 +3664,7 @@
         <v>7</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -3700,7 +3700,7 @@
         <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>6</v>
@@ -3741,19 +3741,19 @@
         <v>9</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3786,7 +3786,7 @@
         <v>8</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -3818,7 +3818,7 @@
         <v>7</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -3830,7 +3830,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3886,7 +3886,7 @@
         <v>7</v>
       </c>
       <c r="F41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="G41">
         <v>10</v>
@@ -3895,19 +3895,19 @@
         <v>7</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3931,19 +3931,19 @@
         <v>8</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>6</v>
       </c>
       <c r="W41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y41">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3972,19 +3972,19 @@
         <v>9</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4014,10 +4014,10 @@
         <v>9</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y42">
         <v>10</v>
@@ -4055,7 +4055,7 @@
         <v>-1</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L43">
         <v>-1</v>
@@ -4132,7 +4132,7 @@
         <v>-1</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L44">
         <v>-1</v>
@@ -4239,25 +4239,25 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>34.15</v>
+        <v>53.66</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J2">
-        <v>65.84999999999999</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4303,25 +4303,25 @@
         <v>41</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="G4">
-        <v>9.76</v>
+        <v>7.32</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>17.07</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4335,30 +4335,30 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="I5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4367,19 +4367,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6">
-        <v>87.8</v>
+        <v>85.37</v>
       </c>
       <c r="G6">
-        <v>12.2</v>
+        <v>14.63</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4390,7 +4390,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>67</v>
@@ -4399,19 +4399,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>90.23999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="G7">
-        <v>9.76</v>
+        <v>12.2</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4427,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4456,16 +4456,16 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920388</v>
+        <v>21330051920029</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4476,16 +4476,16 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920029</v>
+        <v>21330051920030</v>
       </c>
       <c r="B3" t="s">
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4499,19 +4499,19 @@
         <v>21330051920030</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4519,53 +4519,53 @@
         <v>21330051920030</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920030</v>
+        <v>21330051920036</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920031</v>
+        <v>21330051920037</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4576,36 +4576,36 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920032</v>
+        <v>21330051920039</v>
       </c>
       <c r="B8" t="s">
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920034</v>
+        <v>21330051920041</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -4616,16 +4616,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920035</v>
+        <v>21330051920046</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -4636,16 +4636,16 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920036</v>
+        <v>21330051920047</v>
       </c>
       <c r="B11" t="s">
         <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -4656,36 +4656,36 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920037</v>
+        <v>21330051920047</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>21330051920038</v>
+        <v>21330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -4696,16 +4696,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920038</v>
+        <v>21330051920052</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -4716,36 +4716,36 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920390</v>
+        <v>21330051920052</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920039</v>
+        <v>21330051920053</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -4756,16 +4756,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920041</v>
+        <v>21330051920054</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -4776,56 +4776,56 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920043</v>
+        <v>21330051920057</v>
       </c>
       <c r="B18" t="s">
         <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920046</v>
+        <v>21330051920057</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920047</v>
+        <v>21330051920058</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -4836,96 +4836,96 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920047</v>
+        <v>21330051920061</v>
       </c>
       <c r="B21" t="s">
         <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920052</v>
+        <v>21330051920061</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920052</v>
+        <v>21330051920061</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920052</v>
+        <v>21330051920062</v>
       </c>
       <c r="B24" t="s">
         <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920053</v>
+        <v>21330051920067</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -4936,16 +4936,16 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920054</v>
+        <v>21330051920069</v>
       </c>
       <c r="B26" t="s">
         <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
         <v>9</v>
@@ -4956,381 +4956,101 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920057</v>
+        <v>21330051920069</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
         <v>99</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920057</v>
+        <v>21330051920069</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
         <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>21330051920057</v>
+        <v>21330051920070</v>
       </c>
       <c r="B29" t="s">
         <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>21330051920058</v>
+        <v>21330051920070</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>21330051920059</v>
+        <v>21330051920070</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>21330051920060</v>
-      </c>
-      <c r="B32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C32" t="s">
-        <v>112</v>
-      </c>
-      <c r="D32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>21330051920061</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" t="s">
-        <v>141</v>
-      </c>
-      <c r="E33" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>21330051920061</v>
-      </c>
-      <c r="B34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>21330051920061</v>
-      </c>
-      <c r="B35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>21330051920062</v>
-      </c>
-      <c r="B36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" t="s">
-        <v>89</v>
-      </c>
-      <c r="D36" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>21330051920062</v>
-      </c>
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" t="s">
-        <v>142</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>21330051920065</v>
-      </c>
-      <c r="B38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38" t="s">
-        <v>143</v>
-      </c>
-      <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>21330051920067</v>
-      </c>
-      <c r="B39" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E39" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>21330051920069</v>
-      </c>
-      <c r="B40" t="s">
-        <v>96</v>
-      </c>
-      <c r="C40" t="s">
-        <v>116</v>
-      </c>
-      <c r="D40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>21330051920069</v>
-      </c>
-      <c r="B41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>116</v>
-      </c>
-      <c r="D41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>21330051920069</v>
-      </c>
-      <c r="B42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C42" t="s">
-        <v>116</v>
-      </c>
-      <c r="D42" t="s">
-        <v>145</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>21330051920070</v>
-      </c>
-      <c r="B43" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" t="s">
-        <v>117</v>
-      </c>
-      <c r="D43" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>21330051920070</v>
-      </c>
-      <c r="B44" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" t="s">
-        <v>117</v>
-      </c>
-      <c r="D44" t="s">
-        <v>146</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>21330051920070</v>
-      </c>
-      <c r="B45" t="s">
-        <v>97</v>
-      </c>
-      <c r="C45" t="s">
-        <v>117</v>
-      </c>
-      <c r="D45" t="s">
-        <v>146</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5370,13 +5090,13 @@
         <v>21330051920030</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5387,13 +5107,13 @@
         <v>21330051920052</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5401,16 +5121,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5418,16 +5138,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920061</v>
+        <v>21330051920069</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5435,16 +5155,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5452,33 +5172,33 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920070</v>
+        <v>21330051920047</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>108</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920038</v>
+        <v>21330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -5486,50 +5206,50 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920047</v>
+        <v>21330051920029</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920062</v>
+        <v>21330051920036</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920388</v>
+        <v>21330051920037</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5537,16 +5257,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920029</v>
+        <v>21330051920039</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5554,16 +5274,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920031</v>
+        <v>21330051920041</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5571,16 +5291,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920032</v>
+        <v>21330051920046</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -5588,16 +5308,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920034</v>
+        <v>21330051920053</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -5605,16 +5325,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920035</v>
+        <v>21330051920054</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5622,16 +5342,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920036</v>
+        <v>21330051920058</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5639,16 +5359,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920037</v>
+        <v>21330051920062</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5656,16 +5376,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920390</v>
+        <v>21330051920067</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5673,200 +5393,200 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920039</v>
+        <v>21330051920388</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="D20" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920041</v>
+        <v>21330051920031</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920043</v>
+        <v>21330051920032</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920046</v>
+        <v>21330051920033</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920053</v>
+        <v>21330051920034</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920054</v>
+        <v>21330051920035</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920058</v>
+        <v>21330051920038</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920059</v>
+        <v>21330051920390</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920060</v>
+        <v>21330051920040</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="D28" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920065</v>
+        <v>21330051920043</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920067</v>
+        <v>21330051920045</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C30" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920033</v>
+        <v>21330051920048</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="D31" t="s">
         <v>163</v>
@@ -5877,13 +5597,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920040</v>
+        <v>21330051920050</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="D32" t="s">
         <v>164</v>
@@ -5894,13 +5614,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920045</v>
+        <v>21330051920049</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
         <v>165</v>
@@ -5911,13 +5631,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920048</v>
+        <v>21330051920051</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="D34" t="s">
         <v>166</v>
@@ -5928,13 +5648,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920050</v>
+        <v>21330051920055</v>
       </c>
       <c r="B35" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D35" t="s">
         <v>167</v>
@@ -5945,13 +5665,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920049</v>
+        <v>21330051920056</v>
       </c>
       <c r="B36" t="s">
-        <v>150</v>
+        <v>99</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
         <v>168</v>
@@ -5962,13 +5682,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920051</v>
+        <v>21330051920059</v>
       </c>
       <c r="B37" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
         <v>169</v>
@@ -5979,13 +5699,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920055</v>
+        <v>21330051920060</v>
       </c>
       <c r="B38" t="s">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="C38" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="D38" t="s">
         <v>170</v>
@@ -5996,13 +5716,13 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920056</v>
+        <v>21330051920063</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D39" t="s">
         <v>171</v>
@@ -6013,13 +5733,13 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920063</v>
+        <v>21330051920064</v>
       </c>
       <c r="B40" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>161</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
         <v>172</v>
@@ -6030,13 +5750,13 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920064</v>
+        <v>21330051920065</v>
       </c>
       <c r="B41" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
         <v>173</v>
@@ -6050,13 +5770,13 @@
         <v>21330051920066</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C42" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D42" t="s">
-        <v>139</v>
+        <v>169</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -6069,7 +5789,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6104,13 +5824,13 @@
         <v>21330051920032</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6127,22 +5847,22 @@
         <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -6150,13 +5870,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
         <v>104</v>
-      </c>
-      <c r="D4" t="s">
-        <v>126</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6173,13 +5893,13 @@
         <v>21330051920037</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" t="s">
         <v>104</v>
-      </c>
-      <c r="D5" t="s">
-        <v>126</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -6193,39 +5913,39 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920062</v>
+        <v>21330051920041</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920062</v>
+        <v>21330051920041</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6242,13 +5962,13 @@
         <v>21330051920388</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="D8" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -6257,7 +5977,7 @@
         <v>62</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -6265,13 +5985,13 @@
         <v>21330051920029</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -6285,16 +6005,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920031</v>
+        <v>21330051920036</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -6308,39 +6028,39 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920034</v>
+        <v>21330051920038</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="D11" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920035</v>
+        <v>21330051920039</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -6354,16 +6074,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920036</v>
+        <v>21330051920046</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -6377,39 +6097,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920390</v>
+        <v>21330051920048</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="D14" t="s">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920039</v>
+        <v>21330051920054</v>
       </c>
       <c r="B15" t="s">
         <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -6423,16 +6143,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920041</v>
+        <v>21330051920058</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -6446,22 +6166,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920043</v>
+        <v>21330051920062</v>
       </c>
       <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
         <v>83</v>
       </c>
-      <c r="C17" t="s">
-        <v>108</v>
-      </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G17">
         <v>-1</v>
@@ -6469,16 +6189,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>21330051920046</v>
+        <v>21330051920067</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -6487,190 +6207,6 @@
         <v>62</v>
       </c>
       <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>21330051920048</v>
-      </c>
-      <c r="B19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>21330051920051</v>
-      </c>
-      <c r="B20" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" t="s">
-        <v>158</v>
-      </c>
-      <c r="D20" t="s">
-        <v>169</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>21330051920054</v>
-      </c>
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>21330051920058</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>21330051920059</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>21330051920060</v>
-      </c>
-      <c r="B24" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>21330051920065</v>
-      </c>
-      <c r="B25" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" t="s">
-        <v>114</v>
-      </c>
-      <c r="D25" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>21330051920067</v>
-      </c>
-      <c r="B26" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -254,259 +254,259 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
   </si>
   <si>
     <t>SIERRA</t>
   </si>
   <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>ZENON AXXEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
   </si>
   <si>
     <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
   </si>
   <si>
     <t>MICHEL</t>
@@ -2346,7 +2346,7 @@
         <v>7</v>
       </c>
       <c r="F21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G21">
         <v>10</v>
@@ -2364,7 +2364,7 @@
         <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2400,7 +2400,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2749,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -4239,13 +4239,13 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>53.66</v>
+        <v>56.1</v>
       </c>
       <c r="G2">
         <v>2.44</v>
@@ -4254,10 +4254,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J2">
-        <v>43.9</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4427,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4462,10 +4462,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4482,10 +4482,10 @@
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4502,10 +4502,10 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4522,10 +4522,10 @@
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -4542,10 +4542,10 @@
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -4562,10 +4562,10 @@
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4582,10 +4582,10 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -4602,10 +4602,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -4616,16 +4616,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>21330051920046</v>
+        <v>21330051920047</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -4639,39 +4639,39 @@
         <v>21330051920047</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>21330051920047</v>
+        <v>21330051920052</v>
       </c>
       <c r="B12" t="s">
         <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4679,19 +4679,19 @@
         <v>21330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4699,53 +4699,53 @@
         <v>21330051920052</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B15" t="s">
         <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920053</v>
+        <v>21330051920054</v>
       </c>
       <c r="B16" t="s">
         <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -4756,16 +4756,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920054</v>
+        <v>21330051920057</v>
       </c>
       <c r="B17" t="s">
         <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -4779,53 +4779,53 @@
         <v>21330051920057</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920057</v>
+        <v>21330051920058</v>
       </c>
       <c r="B19" t="s">
         <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>21330051920058</v>
+        <v>21330051920061</v>
       </c>
       <c r="B20" t="s">
         <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -4839,19 +4839,19 @@
         <v>21330051920061</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -4859,53 +4859,53 @@
         <v>21330051920061</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B23" t="s">
         <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B24" t="s">
         <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -4916,16 +4916,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>21330051920067</v>
+        <v>21330051920069</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -4939,19 +4939,19 @@
         <v>21330051920069</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -4959,39 +4959,39 @@
         <v>21330051920069</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B28" t="s">
         <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4999,19 +4999,19 @@
         <v>21330051920070</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -5019,38 +5019,18 @@
         <v>21330051920070</v>
       </c>
       <c r="B30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>21330051920070</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5093,10 +5073,10 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5107,13 +5087,13 @@
         <v>21330051920052</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5124,13 +5104,13 @@
         <v>21330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5141,13 +5121,13 @@
         <v>21330051920069</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5158,13 +5138,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5175,13 +5155,13 @@
         <v>21330051920047</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -5192,13 +5172,13 @@
         <v>21330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -5212,10 +5192,10 @@
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5229,10 +5209,10 @@
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -5246,10 +5226,10 @@
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -5263,10 +5243,10 @@
         <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5280,10 +5260,10 @@
         <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5291,13 +5271,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920046</v>
+        <v>21330051920053</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -5308,16 +5288,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920053</v>
+        <v>21330051920054</v>
       </c>
       <c r="B15" t="s">
         <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -5325,16 +5305,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920054</v>
+        <v>21330051920058</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5342,16 +5322,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920058</v>
+        <v>21330051920062</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5359,16 +5339,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B18" t="s">
         <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5376,30 +5356,30 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920067</v>
+        <v>21330051920388</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="D19" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920388</v>
+        <v>21330051920031</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D20" t="s">
         <v>152</v>
@@ -5410,13 +5390,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920031</v>
+        <v>21330051920032</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
         <v>153</v>
@@ -5427,13 +5407,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920032</v>
+        <v>21330051920033</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="D22" t="s">
         <v>154</v>
@@ -5444,13 +5424,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920033</v>
+        <v>21330051920034</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D23" t="s">
         <v>155</v>
@@ -5461,13 +5441,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920034</v>
+        <v>21330051920035</v>
       </c>
       <c r="B24" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
         <v>156</v>
@@ -5478,13 +5458,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920035</v>
+        <v>21330051920038</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
         <v>157</v>
@@ -5495,13 +5475,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920038</v>
+        <v>21330051920390</v>
       </c>
       <c r="B26" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D26" t="s">
         <v>158</v>
@@ -5512,13 +5492,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920390</v>
+        <v>21330051920040</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D27" t="s">
         <v>159</v>
@@ -5529,13 +5509,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920040</v>
+        <v>21330051920043</v>
       </c>
       <c r="B28" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D28" t="s">
         <v>160</v>
@@ -5546,13 +5526,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920043</v>
+        <v>21330051920045</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
         <v>161</v>
@@ -5563,13 +5543,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920045</v>
+        <v>21330051920046</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
         <v>162</v>
@@ -5583,10 +5563,10 @@
         <v>21330051920048</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
         <v>163</v>
@@ -5600,10 +5580,10 @@
         <v>21330051920050</v>
       </c>
       <c r="B32" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D32" t="s">
         <v>164</v>
@@ -5617,10 +5597,10 @@
         <v>21330051920049</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
         <v>165</v>
@@ -5634,10 +5614,10 @@
         <v>21330051920051</v>
       </c>
       <c r="B34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D34" t="s">
         <v>166</v>
@@ -5651,10 +5631,10 @@
         <v>21330051920055</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D35" t="s">
         <v>167</v>
@@ -5668,10 +5648,10 @@
         <v>21330051920056</v>
       </c>
       <c r="B36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
         <v>168</v>
@@ -5685,10 +5665,10 @@
         <v>21330051920059</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D37" t="s">
         <v>169</v>
@@ -5702,10 +5682,10 @@
         <v>21330051920060</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D38" t="s">
         <v>170</v>
@@ -5719,10 +5699,10 @@
         <v>21330051920063</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C39" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D39" t="s">
         <v>171</v>
@@ -5736,7 +5716,7 @@
         <v>21330051920064</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C40" t="s">
         <v>76</v>
@@ -5753,10 +5733,10 @@
         <v>21330051920065</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
         <v>173</v>
@@ -5770,10 +5750,10 @@
         <v>21330051920066</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
         <v>169</v>
@@ -5789,7 +5769,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5824,13 +5804,13 @@
         <v>21330051920032</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5847,13 +5827,13 @@
         <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -5873,10 +5853,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5896,10 +5876,10 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5919,10 +5899,10 @@
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5942,10 +5922,10 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5962,13 +5942,13 @@
         <v>21330051920388</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5988,10 +5968,10 @@
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -6011,10 +5991,10 @@
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -6031,13 +6011,13 @@
         <v>21330051920038</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C11" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -6057,10 +6037,10 @@
         <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -6074,62 +6054,62 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920046</v>
+        <v>21330051920048</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>163</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920054</v>
+        <v>21330051920058</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -6143,16 +6123,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920058</v>
+        <v>21330051920062</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -6166,16 +6146,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B17" t="s">
         <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -6184,29 +6164,6 @@
         <v>62</v>
       </c>
       <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>21330051920067</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>116</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -1668,7 +1668,7 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L12">
         <v>-1</v>
@@ -1704,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>-1</v>
@@ -2900,7 +2900,7 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2936,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>-1</v>
@@ -3362,7 +3362,7 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3439,7 +3439,7 @@
         <v>6</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -3475,7 +3475,7 @@
         <v>6</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -4379,7 +4379,7 @@
         <v>14.63</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -251,253 +251,253 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OREA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TLAXCALTECALT</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>VILLANUEVA</t>
+  </si>
+  <si>
+    <t>ZETINA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DEL ROSARIO</t>
+  </si>
+  <si>
+    <t>ESTRADA</t>
+  </si>
+  <si>
+    <t>LEPE</t>
+  </si>
+  <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>MARISOL</t>
+  </si>
+  <si>
+    <t>PATRICIA</t>
+  </si>
+  <si>
+    <t>ALEJANDRO GABRIEL</t>
+  </si>
+  <si>
+    <t>CARLA ESTEFANIA</t>
+  </si>
+  <si>
+    <t>LAURA FERNANDA</t>
+  </si>
+  <si>
+    <t>NUBIA NAHOMI</t>
+  </si>
+  <si>
+    <t>DAIRA</t>
+  </si>
+  <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>INGRID CRISTEL</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>DARINKA PAOLA</t>
+  </si>
+  <si>
+    <t>KARLA JAZMIN</t>
+  </si>
+  <si>
+    <t>HANIA ZARETH</t>
+  </si>
+  <si>
+    <t>JOHANA RUBI</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OREA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TLAXCALTECALT</t>
-  </si>
-  <si>
-    <t>VEGA</t>
-  </si>
-  <si>
-    <t>VILLANUEVA</t>
-  </si>
-  <si>
-    <t>ZETINA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DEL ROSARIO</t>
-  </si>
-  <si>
-    <t>ESTRADA</t>
-  </si>
-  <si>
-    <t>LEPE</t>
-  </si>
-  <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
-  </si>
-  <si>
-    <t>PATRICIA</t>
-  </si>
-  <si>
-    <t>ALEJANDRO GABRIEL</t>
-  </si>
-  <si>
-    <t>CARLA ESTEFANIA</t>
-  </si>
-  <si>
-    <t>LAURA FERNANDA</t>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
+    <t>ZENON AXXEL</t>
   </si>
   <si>
     <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>NUBIA NAHOMI</t>
-  </si>
-  <si>
-    <t>DAIRA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>INGRID CRISTEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>DARINKA PAOLA</t>
-  </si>
-  <si>
-    <t>KARLA JAZMIN</t>
-  </si>
-  <si>
-    <t>HANIA ZARETH</t>
-  </si>
-  <si>
-    <t>JOHANA RUBI</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
   </si>
   <si>
     <t>EMMANUEL DAVID</t>
@@ -1061,7 +1061,7 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1070,16 +1070,16 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -1091,7 +1091,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>8</v>
@@ -1129,16 +1129,16 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1147,13 +1147,13 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1165,13 +1165,13 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5">
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1206,16 +1206,16 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1224,13 +1224,13 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1289,10 +1289,10 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1301,13 +1301,13 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1319,7 +1319,7 @@
         <v>6</v>
       </c>
       <c r="W7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1366,10 +1366,10 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1378,16 +1378,16 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1396,13 +1396,13 @@
         <v>6</v>
       </c>
       <c r="W8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>5</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1446,7 +1446,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1455,13 +1455,13 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1473,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>10</v>
@@ -1523,7 +1523,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1532,16 +1532,16 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>10</v>
@@ -1550,7 +1550,7 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1591,16 +1591,16 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1609,13 +1609,13 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1627,7 +1627,7 @@
         <v>6</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1674,10 +1674,10 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1686,13 +1686,13 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1704,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>-1</v>
@@ -1745,16 +1745,16 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1763,16 +1763,16 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1781,13 +1781,13 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>-1</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1831,7 +1831,7 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1840,16 +1840,16 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1861,7 +1861,7 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1908,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1917,16 +1917,16 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>10</v>
@@ -1938,7 +1938,7 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1982,10 +1982,10 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1994,16 +1994,16 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>8</v>
@@ -2012,13 +2012,13 @@
         <v>6</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X16">
         <v>-1</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2062,7 +2062,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2071,13 +2071,13 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2095,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2115,7 +2115,7 @@
         <v>6</v>
       </c>
       <c r="F18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G18">
         <v>10</v>
@@ -2133,13 +2133,13 @@
         <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2148,13 +2148,13 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2166,10 +2166,10 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2216,7 +2216,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2225,13 +2225,13 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2246,7 +2246,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>10</v>
@@ -2287,13 +2287,13 @@
         <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2302,13 +2302,13 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2323,10 +2323,10 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2370,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2379,13 +2379,13 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2447,7 +2447,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2456,16 +2456,16 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2521,10 +2521,10 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2533,16 +2533,16 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2601,7 +2601,7 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2610,13 +2610,13 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
@@ -2678,7 +2678,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2687,13 +2687,13 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2708,7 +2708,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2755,7 +2755,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2764,16 +2764,16 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2782,7 +2782,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2829,10 +2829,10 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2841,13 +2841,13 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T27">
         <v>5</v>
@@ -2906,10 +2906,10 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2918,13 +2918,13 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -2936,13 +2936,13 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>-1</v>
       </c>
       <c r="Y28">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2983,10 +2983,10 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2995,16 +2995,16 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -3019,7 +3019,7 @@
         <v>-1</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3063,7 +3063,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3072,16 +3072,16 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3096,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3140,7 +3140,7 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3149,13 +3149,13 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -3170,7 +3170,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3217,7 +3217,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3226,13 +3226,13 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3291,10 +3291,10 @@
         <v>7</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3303,16 +3303,16 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R33">
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3347,7 +3347,7 @@
         <v>5</v>
       </c>
       <c r="F34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G34">
         <v>5</v>
@@ -3365,13 +3365,13 @@
         <v>6</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3380,13 +3380,13 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>5</v>
@@ -3398,13 +3398,13 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3448,7 +3448,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3457,16 +3457,16 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3522,10 +3522,10 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3534,13 +3534,13 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T36">
         <v>5</v>
@@ -3602,7 +3602,7 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3611,13 +3611,13 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>7</v>
@@ -3632,7 +3632,7 @@
         <v>7</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3676,10 +3676,10 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3688,16 +3688,16 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>7</v>
@@ -3706,7 +3706,7 @@
         <v>6</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>-1</v>
@@ -3756,7 +3756,7 @@
         <v>7</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3765,16 +3765,16 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R39">
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>10</v>
@@ -3783,7 +3783,7 @@
         <v>6</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X39">
         <v>9</v>
@@ -3833,7 +3833,7 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -3842,13 +3842,13 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R40">
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>8</v>
@@ -3910,7 +3910,7 @@
         <v>8</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -3919,13 +3919,13 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T41">
         <v>8</v>
@@ -3987,7 +3987,7 @@
         <v>10</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -3996,13 +3996,13 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>10</v>
@@ -4061,10 +4061,10 @@
         <v>-1</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>-1</v>
@@ -4073,13 +4073,13 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R43">
         <v>-1</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T43">
         <v>5</v>
@@ -4138,10 +4138,10 @@
         <v>-1</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O44">
         <v>-1</v>
@@ -4150,13 +4150,13 @@
         <v>-1</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R44">
         <v>-1</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T44">
         <v>5</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="Y44">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4239,25 +4239,25 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>56.1</v>
+        <v>60.98</v>
       </c>
       <c r="G2">
         <v>2.44</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2">
-        <v>41.46</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4271,19 +4271,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>73.17</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="G3">
-        <v>26.83</v>
+        <v>19.51</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4379,7 +4379,7 @@
         <v>14.63</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4399,19 +4399,19 @@
         <v>41</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>87.8</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="G7">
-        <v>12.2</v>
+        <v>7.32</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4427,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4462,10 +4462,10 @@
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -4482,10 +4482,10 @@
         <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4502,10 +4502,10 @@
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4522,10 +4522,10 @@
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -4542,10 +4542,10 @@
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -4562,10 +4562,10 @@
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -4582,10 +4582,10 @@
         <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -4596,16 +4596,16 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>21330051920041</v>
+        <v>21330051920047</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -4619,39 +4619,39 @@
         <v>21330051920047</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>21330051920047</v>
+        <v>21330051920052</v>
       </c>
       <c r="B11" t="s">
         <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4659,19 +4659,19 @@
         <v>21330051920052</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4679,53 +4679,53 @@
         <v>21330051920052</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>21330051920052</v>
+        <v>21330051920053</v>
       </c>
       <c r="B14" t="s">
         <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>21330051920053</v>
+        <v>21330051920054</v>
       </c>
       <c r="B15" t="s">
         <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
@@ -4736,36 +4736,36 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>21330051920054</v>
+        <v>21330051920057</v>
       </c>
       <c r="B16" t="s">
         <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>21330051920057</v>
+        <v>21330051920058</v>
       </c>
       <c r="B17" t="s">
         <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -4776,42 +4776,42 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>21330051920057</v>
+        <v>21330051920061</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
         <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>21330051920058</v>
+        <v>21330051920061</v>
       </c>
       <c r="B19" t="s">
         <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -4819,47 +4819,47 @@
         <v>21330051920061</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>21330051920061</v>
+        <v>21330051920062</v>
       </c>
       <c r="B21" t="s">
         <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>21330051920061</v>
+        <v>21330051920067</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
         <v>95</v>
@@ -4868,21 +4868,21 @@
         <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>21330051920062</v>
+        <v>21330051920069</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>21330051920067</v>
+        <v>21330051920069</v>
       </c>
       <c r="B24" t="s">
         <v>86</v>
@@ -4905,13 +4905,13 @@
         <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4919,24 +4919,24 @@
         <v>21330051920069</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B26" t="s">
         <v>87</v>
@@ -4945,18 +4945,18 @@
         <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>21330051920069</v>
+        <v>21330051920070</v>
       </c>
       <c r="B27" t="s">
         <v>87</v>
@@ -4965,13 +4965,13 @@
         <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4979,58 +4979,18 @@
         <v>21330051920070</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>21330051920070</v>
-      </c>
-      <c r="B29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" t="s">
-        <v>98</v>
-      </c>
-      <c r="D29" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>21330051920070</v>
-      </c>
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" t="s">
-        <v>115</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
         <v>64</v>
       </c>
     </row>
@@ -5073,10 +5033,10 @@
         <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -5087,13 +5047,13 @@
         <v>21330051920052</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -5104,13 +5064,13 @@
         <v>21330051920061</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -5121,13 +5081,13 @@
         <v>21330051920069</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -5138,13 +5098,13 @@
         <v>21330051920070</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5155,13 +5115,13 @@
         <v>21330051920047</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -5169,33 +5129,33 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920057</v>
+        <v>21330051920029</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920029</v>
+        <v>21330051920036</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -5203,10 +5163,10 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920036</v>
+        <v>21330051920037</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
         <v>91</v>
@@ -5220,10 +5180,10 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920037</v>
+        <v>21330051920039</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
         <v>92</v>
@@ -5237,16 +5197,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920039</v>
+        <v>21330051920053</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -5254,16 +5214,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920041</v>
+        <v>21330051920054</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
         <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -5271,13 +5231,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920053</v>
+        <v>21330051920057</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>107</v>
@@ -5288,13 +5248,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920054</v>
+        <v>21330051920058</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>108</v>
@@ -5305,13 +5265,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920058</v>
+        <v>21330051920062</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D16" t="s">
         <v>110</v>
@@ -5322,16 +5282,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B17" t="s">
         <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5339,27 +5299,27 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920067</v>
+        <v>21330051920388</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920388</v>
+        <v>21330051920031</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
         <v>133</v>
@@ -5373,13 +5333,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920031</v>
+        <v>21330051920032</v>
       </c>
       <c r="B20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
         <v>152</v>
@@ -5390,13 +5350,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920032</v>
+        <v>21330051920033</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="D21" t="s">
         <v>153</v>
@@ -5407,10 +5367,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920033</v>
+        <v>21330051920034</v>
       </c>
       <c r="B22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
         <v>135</v>
@@ -5424,13 +5384,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920034</v>
+        <v>21330051920035</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
         <v>155</v>
@@ -5441,13 +5401,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920035</v>
+        <v>21330051920038</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
         <v>156</v>
@@ -5458,10 +5418,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920038</v>
+        <v>21330051920390</v>
       </c>
       <c r="B25" t="s">
-        <v>122</v>
+        <v>76</v>
       </c>
       <c r="C25" t="s">
         <v>137</v>
@@ -5475,13 +5435,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920390</v>
+        <v>21330051920040</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
         <v>158</v>
@@ -5492,13 +5452,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920040</v>
+        <v>21330051920041</v>
       </c>
       <c r="B27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
         <v>159</v>
@@ -5512,10 +5472,10 @@
         <v>21330051920043</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="C28" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D28" t="s">
         <v>160</v>
@@ -5529,10 +5489,10 @@
         <v>21330051920045</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D29" t="s">
         <v>161</v>
@@ -5546,10 +5506,10 @@
         <v>21330051920046</v>
       </c>
       <c r="B30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
         <v>162</v>
@@ -5563,10 +5523,10 @@
         <v>21330051920048</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D31" t="s">
         <v>163</v>
@@ -5580,10 +5540,10 @@
         <v>21330051920050</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s">
         <v>164</v>
@@ -5597,10 +5557,10 @@
         <v>21330051920049</v>
       </c>
       <c r="B33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
         <v>165</v>
@@ -5614,10 +5574,10 @@
         <v>21330051920051</v>
       </c>
       <c r="B34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
         <v>166</v>
@@ -5631,10 +5591,10 @@
         <v>21330051920055</v>
       </c>
       <c r="B35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
         <v>167</v>
@@ -5648,10 +5608,10 @@
         <v>21330051920056</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D36" t="s">
         <v>168</v>
@@ -5665,10 +5625,10 @@
         <v>21330051920059</v>
       </c>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
         <v>169</v>
@@ -5682,10 +5642,10 @@
         <v>21330051920060</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
         <v>170</v>
@@ -5699,10 +5659,10 @@
         <v>21330051920063</v>
       </c>
       <c r="B39" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D39" t="s">
         <v>171</v>
@@ -5716,7 +5676,7 @@
         <v>21330051920064</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C40" t="s">
         <v>76</v>
@@ -5733,10 +5693,10 @@
         <v>21330051920065</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
         <v>173</v>
@@ -5750,10 +5710,10 @@
         <v>21330051920066</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D42" t="s">
         <v>169</v>
@@ -5769,7 +5729,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5801,22 +5761,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920032</v>
+        <v>21330051920388</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5824,22 +5784,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920032</v>
+        <v>21330051920388</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5853,10 +5813,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5876,10 +5836,10 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5893,16 +5853,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920041</v>
+        <v>21330051920039</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -5916,16 +5876,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920041</v>
+        <v>21330051920039</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5939,22 +5899,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920388</v>
+        <v>21330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5962,22 +5922,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920029</v>
+        <v>21330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5985,16 +5945,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920036</v>
+        <v>21330051920029</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -6008,16 +5968,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920038</v>
+        <v>21330051920032</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
@@ -6031,16 +5991,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920039</v>
+        <v>21330051920036</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -6054,36 +6014,36 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920048</v>
+        <v>21330051920054</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920054</v>
+        <v>21330051920058</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
         <v>108</v>
@@ -6100,13 +6060,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920058</v>
+        <v>21330051920062</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
         <v>110</v>
@@ -6123,16 +6083,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>21330051920062</v>
+        <v>21330051920067</v>
       </c>
       <c r="B16" t="s">
         <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E16" t="s">
         <v>9</v>
@@ -6141,29 +6101,6 @@
         <v>62</v>
       </c>
       <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920067</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>113</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2ARHV - Estadisticos 20212.xlsx
+++ b/grupos/2ARHV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -209,18 +209,18 @@
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
@@ -236,24 +236,69 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ARAGON</t>
+  </si>
+  <si>
     <t>ANDRADE</t>
   </si>
   <si>
     <t>ALVARADO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>AQUINO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>COMIHUA</t>
   </si>
   <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>NAJERA</t>
   </si>
   <si>
@@ -263,18 +308,36 @@
     <t>ORTIZ</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>ROMAN</t>
   </si>
   <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
     <t>TLAXCALTECALT</t>
   </si>
   <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>VEGA</t>
   </si>
   <si>
@@ -284,10 +347,16 @@
     <t>ZETINA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
   </si>
   <si>
     <t>SANCHEZ</t>
@@ -296,42 +365,132 @@
     <t>DEL ROSARIO</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CELESTINO</t>
+  </si>
+  <si>
     <t>ESTRADA</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>SIERRA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>TETLACTLE</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
     <t>LEPE</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
     <t>RANGEL</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>VALLEJO</t>
   </si>
   <si>
+    <t>JONATHAN YOSEF</t>
+  </si>
+  <si>
     <t>MARISOL</t>
   </si>
   <si>
     <t>PATRICIA</t>
   </si>
   <si>
+    <t>ALESSANDRA</t>
+  </si>
+  <si>
+    <t>BETSI JOSELIN</t>
+  </si>
+  <si>
+    <t>GUADALUPE JOSELYNE</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>GABRIELA ELIZABETH</t>
+  </si>
+  <si>
     <t>ALEJANDRO GABRIEL</t>
   </si>
   <si>
     <t>CARLA ESTEFANIA</t>
   </si>
   <si>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>KARLA JIMENA</t>
+  </si>
+  <si>
     <t>LAURA FERNANDA</t>
   </si>
   <si>
+    <t>ZENON AXXEL</t>
+  </si>
+  <si>
+    <t>GIOVANI</t>
+  </si>
+  <si>
+    <t>EMMANUEL DAVID</t>
+  </si>
+  <si>
+    <t>ZURY BETZABE</t>
+  </si>
+  <si>
+    <t>MIA ARANZA</t>
+  </si>
+  <si>
     <t>NUBIA NAHOMI</t>
   </si>
   <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>AMY</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
     <t>DAIRA</t>
   </si>
   <si>
@@ -341,18 +500,39 @@
     <t>ANGEL GABRIEL</t>
   </si>
   <si>
+    <t>MARIEL</t>
+  </si>
+  <si>
+    <t>ANDREA YONETH</t>
+  </si>
+  <si>
     <t>INGRID CRISTEL</t>
   </si>
   <si>
     <t>MARIANA</t>
   </si>
   <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
+    <t>SARAHI</t>
+  </si>
+  <si>
     <t>DARINKA PAOLA</t>
   </si>
   <si>
     <t>KARLA JAZMIN</t>
   </si>
   <si>
+    <t>YAZURI</t>
+  </si>
+  <si>
+    <t>ANIELKA</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
     <t>HANIA ZARETH</t>
   </si>
   <si>
@@ -360,186 +540,6 @@
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>ARAGON</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>AQUINO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>BRUNO</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>CELESTINO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>SIERRA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TETLACTLE</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JONATHAN YOSEF</t>
-  </si>
-  <si>
-    <t>ALESSANDRA</t>
-  </si>
-  <si>
-    <t>BETSI JOSELIN</t>
-  </si>
-  <si>
-    <t>GUADALUPE JOSELYNE</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>GABRIELA ELIZABETH</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>KARLA JIMENA</t>
-  </si>
-  <si>
-    <t>ZENON AXXEL</t>
-  </si>
-  <si>
-    <t>GIOVANI</t>
-  </si>
-  <si>
-    <t>EMMANUEL DAVID</t>
-  </si>
-  <si>
-    <t>ZURY BETZABE</t>
-  </si>
-  <si>
-    <t>MIA ARANZA</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>AMY</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>ANDREA YONETH</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SARAHI</t>
-  </si>
-  <si>
-    <t>YAZURI</t>
-  </si>
-  <si>
-    <t>ANIELKA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
   </si>
 </sst>
 </file>
@@ -1064,10 +1064,10 @@
         <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -1105,16 +1105,16 @@
         <v>5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G5">
         <v>8</v>
@@ -1123,16 +1123,16 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -1141,16 +1141,16 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q5">
         <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -1159,16 +1159,16 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>5</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
       <c r="F6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -1203,13 +1203,13 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1218,16 +1218,16 @@
         <v>7</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
         <v>10</v>
@@ -1245,7 +1245,7 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1280,13 +1280,13 @@
         <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>8</v>
@@ -1295,16 +1295,16 @@
         <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>8</v>
@@ -1322,7 +1322,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1372,16 +1372,16 @@
         <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -1390,10 +1390,10 @@
         <v>7</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W8">
         <v>5</v>
@@ -1449,10 +1449,10 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1470,7 +1470,7 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1526,10 +1526,10 @@
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>8</v>
@@ -1547,7 +1547,7 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1603,10 +1603,10 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1621,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1653,7 +1653,7 @@
         <v>9</v>
       </c>
       <c r="F12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G12">
         <v>10</v>
@@ -1665,13 +1665,13 @@
         <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>5</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1680,16 +1680,16 @@
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>5</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1698,7 +1698,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1730,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="F13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G13">
         <v>8</v>
@@ -1742,13 +1742,13 @@
         <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>10</v>
@@ -1757,16 +1757,16 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>10</v>
@@ -1775,7 +1775,7 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>6</v>
@@ -1784,7 +1784,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1834,10 +1834,10 @@
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>8</v>
@@ -1855,7 +1855,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1896,7 +1896,7 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -1911,10 +1911,10 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
         <v>7</v>
@@ -1961,7 +1961,7 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G16">
         <v>7</v>
@@ -1973,13 +1973,13 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K16">
         <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -1988,16 +1988,16 @@
         <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -2006,16 +2006,16 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W16">
         <v>5</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
         <v>6</v>
@@ -2065,16 +2065,16 @@
         <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>5</v>
@@ -2092,7 +2092,7 @@
         <v>7</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2127,7 +2127,7 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>5</v>
@@ -2142,10 +2142,10 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>7</v>
@@ -2219,10 +2219,10 @@
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
         <v>7</v>
@@ -2240,7 +2240,7 @@
         <v>8</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2296,10 +2296,10 @@
         <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -2314,7 +2314,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2358,7 +2358,7 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>7</v>
@@ -2373,10 +2373,10 @@
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
         <v>9</v>
@@ -2417,13 +2417,13 @@
         <v>5</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>6</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>10</v>
@@ -2450,16 +2450,16 @@
         <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -2468,16 +2468,16 @@
         <v>6</v>
       </c>
       <c r="U22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2512,13 +2512,13 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>10</v>
@@ -2527,16 +2527,16 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S23">
         <v>10</v>
@@ -2545,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>6</v>
@@ -2554,7 +2554,7 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>10</v>
@@ -2604,10 +2604,10 @@
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -2681,10 +2681,10 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>7</v>
@@ -2758,10 +2758,10 @@
         <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>7</v>
@@ -2799,16 +2799,16 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>6</v>
       </c>
       <c r="F27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -2817,16 +2817,16 @@
         <v>5</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
         <v>5</v>
@@ -2835,16 +2835,16 @@
         <v>5</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S27">
         <v>5</v>
@@ -2853,16 +2853,16 @@
         <v>5</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>5</v>
@@ -2885,7 +2885,7 @@
         <v>8</v>
       </c>
       <c r="F28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>6</v>
@@ -2897,13 +2897,13 @@
         <v>6</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>6</v>
@@ -2912,16 +2912,16 @@
         <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>10</v>
@@ -2930,16 +2930,16 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>7</v>
@@ -2962,7 +2962,7 @@
         <v>7</v>
       </c>
       <c r="F29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G29">
         <v>8</v>
@@ -2974,13 +2974,13 @@
         <v>7</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>10</v>
@@ -2989,16 +2989,16 @@
         <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
         <v>6</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>10</v>
@@ -3010,13 +3010,13 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>6</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -3066,10 +3066,10 @@
         <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
         <v>9</v>
@@ -3087,7 +3087,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -3143,10 +3143,10 @@
         <v>9</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
         <v>8</v>
@@ -3164,7 +3164,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -3193,7 +3193,7 @@
         <v>6</v>
       </c>
       <c r="F32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -3205,13 +3205,13 @@
         <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>7</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3220,16 +3220,16 @@
         <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q32">
         <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>10</v>
@@ -3247,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3282,7 +3282,7 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>7</v>
@@ -3297,16 +3297,16 @@
         <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
         <v>7</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -3341,7 +3341,7 @@
         <v>5</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3359,7 +3359,7 @@
         <v>8</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>6</v>
@@ -3374,10 +3374,10 @@
         <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
         <v>7</v>
@@ -3392,10 +3392,10 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3451,10 +3451,10 @@
         <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
         <v>7</v>
@@ -3492,16 +3492,16 @@
         <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>5</v>
       </c>
       <c r="F36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>5</v>
@@ -3510,16 +3510,16 @@
         <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -3528,16 +3528,16 @@
         <v>5</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>5</v>
@@ -3546,16 +3546,16 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
       </c>
       <c r="X36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y36">
         <v>5</v>
@@ -3590,7 +3590,7 @@
         <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
         <v>8</v>
@@ -3605,10 +3605,10 @@
         <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
         <v>8</v>
@@ -3623,7 +3623,7 @@
         <v>7</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>6</v>
@@ -3655,7 +3655,7 @@
         <v>10</v>
       </c>
       <c r="F38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>10</v>
@@ -3667,13 +3667,13 @@
         <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>9</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>10</v>
@@ -3682,16 +3682,16 @@
         <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
         <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S38">
         <v>10</v>
@@ -3709,7 +3709,7 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>10</v>
@@ -3759,16 +3759,16 @@
         <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q39">
         <v>7</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S39">
         <v>8</v>
@@ -3786,7 +3786,7 @@
         <v>7</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y39">
         <v>8</v>
@@ -3809,7 +3809,7 @@
         <v>9</v>
       </c>
       <c r="F40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G40">
         <v>10</v>
@@ -3821,13 +3821,13 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
         <v>7</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M40">
         <v>10</v>
@@ -3836,16 +3836,16 @@
         <v>7</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>7</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S40">
         <v>10</v>
@@ -3863,7 +3863,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y40">
         <v>10</v>
@@ -3913,10 +3913,10 @@
         <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>7</v>
@@ -3931,7 +3931,7 @@
         <v>8</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>6</v>
@@ -3990,10 +3990,10 @@
         <v>10</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
         <v>8</v>
@@ -4031,16 +4031,16 @@
         <v>5</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E43">
         <v>5</v>
       </c>
       <c r="F43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G43">
         <v>5</v>
@@ -4049,16 +4049,16 @@
         <v>5</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>5</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
         <v>5</v>
@@ -4067,16 +4067,16 @@
         <v>5</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>5</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S43">
         <v>5</v>
@@ -4085,16 +4085,16 @@
         <v>5</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>5</v>
       </c>
       <c r="X43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y43">
         <v>5</v>
@@ -4108,16 +4108,16 @@
         <v>6</v>
       </c>
       <c r="C44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E44">
         <v>5</v>
       </c>
       <c r="F44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G44">
         <v>5</v>
@@ -4126,16 +4126,16 @@
         <v>5</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K44">
         <v>5</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M44">
         <v>6</v>
@@ -4144,16 +4144,16 @@
         <v>5</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q44">
         <v>5</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S44">
         <v>10</v>
@@ -4162,16 +4162,16 @@
         <v>5</v>
       </c>
       <c r="U44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W44">
         <v>5</v>
       </c>
       <c r="X44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y44">
         <v>7</v>
@@ -4239,30 +4239,30 @@
         <v>41</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>60.98</v>
+        <v>70.73</v>
       </c>
       <c r="G2">
-        <v>2.44</v>
+        <v>29.27</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>36.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
@@ -4283,7 +4283,7 @@
         <v>19.51</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -4306,27 +4306,27 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>80.48999999999999</v>
       </c>
       <c r="G4">
-        <v>7.32</v>
+        <v>19.51</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>12.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>65</v>
@@ -4335,30 +4335,30 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>82.93000000000001</v>
+        <v>85.37</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>14.63</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>17.07</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>66</v>
@@ -4367,19 +4367,19 @@
         <v>41</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>85.37</v>
+        <v>87.8</v>
       </c>
       <c r="G6">
-        <v>14.63</v>
+        <v>12.2</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4427,7 +4427,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4452,546 +4452,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920029</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920030</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920030</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920030</v>
-      </c>
-      <c r="B5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920036</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920037</v>
-      </c>
-      <c r="B7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920039</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920047</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>103</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051920047</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D10" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920052</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" t="s">
-        <v>104</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920052</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920052</v>
-      </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920053</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920054</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920057</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920058</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D17" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920061</v>
-      </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>109</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920061</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" t="s">
-        <v>109</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920061</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920062</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" t="s">
-        <v>110</v>
-      </c>
-      <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920067</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>95</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920069</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920069</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920069</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920070</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" t="s">
-        <v>113</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>21330051920070</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>21330051920070</v>
-      </c>
-      <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -5027,285 +4487,285 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920030</v>
+        <v>21330051920388</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920052</v>
+        <v>21330051920029</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920061</v>
+        <v>21330051920030</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920069</v>
+        <v>21330051920031</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920070</v>
+        <v>21330051920032</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920047</v>
+        <v>21330051920033</v>
       </c>
       <c r="B7" t="s">
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920029</v>
+        <v>21330051920034</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920036</v>
+        <v>21330051920035</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920037</v>
+        <v>21330051920036</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920039</v>
+        <v>21330051920037</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920053</v>
+        <v>21330051920038</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920054</v>
+        <v>21330051920390</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920057</v>
+        <v>21330051920039</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920058</v>
+        <v>21330051920040</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920062</v>
+        <v>21330051920041</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920067</v>
+        <v>21330051920043</v>
       </c>
       <c r="B17" t="s">
         <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920388</v>
+        <v>21330051920045</v>
       </c>
       <c r="B18" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
         <v>150</v>
@@ -5316,13 +4776,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920031</v>
+        <v>21330051920046</v>
       </c>
       <c r="B19" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="D19" t="s">
         <v>151</v>
@@ -5333,10 +4793,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920032</v>
+        <v>21330051920047</v>
       </c>
       <c r="B20" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
         <v>88</v>
@@ -5350,13 +4810,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920033</v>
+        <v>21330051920048</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
         <v>153</v>
@@ -5367,13 +4827,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920034</v>
+        <v>21330051920050</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
         <v>154</v>
@@ -5384,13 +4844,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920035</v>
+        <v>21330051920049</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" t="s">
         <v>155</v>
@@ -5401,13 +4861,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920038</v>
+        <v>21330051920051</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D24" t="s">
         <v>156</v>
@@ -5418,13 +4878,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920390</v>
+        <v>21330051920052</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="D25" t="s">
         <v>157</v>
@@ -5435,13 +4895,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920040</v>
+        <v>21330051920053</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
         <v>158</v>
@@ -5452,13 +4912,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920041</v>
+        <v>21330051920054</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
         <v>159</v>
@@ -5469,13 +4929,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920043</v>
+        <v>21330051920055</v>
       </c>
       <c r="B28" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
         <v>160</v>
@@ -5486,13 +4946,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920045</v>
+        <v>21330051920056</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="D29" t="s">
         <v>161</v>
@@ -5503,13 +4963,13 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920046</v>
+        <v>21330051920057</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
         <v>162</v>
@@ -5520,13 +4980,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920048</v>
+        <v>21330051920058</v>
       </c>
       <c r="B31" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>86</v>
       </c>
       <c r="D31" t="s">
         <v>163</v>
@@ -5537,13 +4997,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920050</v>
+        <v>21330051920059</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D32" t="s">
         <v>164</v>
@@ -5554,13 +5014,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920049</v>
+        <v>21330051920060</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
         <v>165</v>
@@ -5571,13 +5031,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920051</v>
+        <v>21330051920061</v>
       </c>
       <c r="B34" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
         <v>166</v>
@@ -5588,13 +5048,13 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920055</v>
+        <v>21330051920062</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
         <v>167</v>
@@ -5605,13 +5065,13 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920056</v>
+        <v>21330051920063</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
         <v>168</v>
@@ -5622,13 +5082,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920059</v>
+        <v>21330051920064</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
         <v>169</v>
@@ -5639,13 +5099,13 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920060</v>
+        <v>21330051920065</v>
       </c>
       <c r="B38" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="D38" t="s">
         <v>170</v>
@@ -5656,16 +5116,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920063</v>
+        <v>21330051920066</v>
       </c>
       <c r="B39" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5673,16 +5133,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920064</v>
+        <v>21330051920067</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="C40" t="s">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -5690,16 +5150,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920065</v>
+        <v>21330051920069</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>97</v>
       </c>
       <c r="D41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5707,16 +5167,16 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42">
-        <v>21330051920066</v>
+        <v>21330051920070</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -5729,7 +5189,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5761,22 +5221,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920388</v>
+        <v>21330051920032</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5784,16 +5244,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920388</v>
+        <v>21330051920032</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -5810,19 +5270,19 @@
         <v>21330051920037</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5830,16 +5290,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920037</v>
+        <v>21330051920047</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>152</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5848,27 +5308,27 @@
         <v>62</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920039</v>
+        <v>21330051920054</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5876,232 +5336,48 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920039</v>
+        <v>21330051920057</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>162</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920057</v>
+        <v>21330051920067</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>171</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920057</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D9" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920029</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920032</v>
-      </c>
-      <c r="B11" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920036</v>
-      </c>
-      <c r="B12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920054</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920058</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920062</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920067</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
